--- a/machine_report.xlsx
+++ b/machine_report.xlsx
@@ -425,49 +425,412 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Machine</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sensor Value</t>
+          <t>Temperature (°C)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Vibration (mm/s)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Current (A)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Failure Risk (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-11T10:36:26Z</t>
+          <t>Exhaust Fan</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>24</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-01-11T10:37:02Z</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-11T10:36:44Z</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>24</v>
+          <t>Refrigerator</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-11T10:37:02Z</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>24</v>
+          <t>Oven</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Washing Machine</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Air Conditioner</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CNC Mill</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hydraulic Pump</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Electric Motor</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Conveyor Belt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CNC Lathe</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>
